--- a/data/trans_dic/P62A$otras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,58</t>
+          <t>0,17; 1,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,24</t>
+          <t>2,43; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,18</t>
+          <t>2,52; 6,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,86; 33,8</t>
+          <t>24,74; 33,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,44</t>
+          <t>2,13; 5,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,2</t>
+          <t>4,52; 9,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 14,71</t>
+          <t>8,27; 15,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 18,33</t>
+          <t>12,83; 18,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,1</t>
+          <t>1,32; 3,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,32</t>
+          <t>3,99; 6,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,74</t>
+          <t>5,67; 9,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 24,08</t>
+          <t>18,76; 23,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 17,86</t>
+          <t>8,99; 17,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,66</t>
+          <t>6,88; 12,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,99; 36,92</t>
+          <t>28,89; 37,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 20,6</t>
+          <t>6,03; 22,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,38; 38,89</t>
+          <t>24,49; 39,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 26,02</t>
+          <t>15,4; 26,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 29,15</t>
+          <t>5,55; 29,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,63</t>
+          <t>2,69; 8,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 24,35</t>
+          <t>16,44; 24,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 16,67</t>
+          <t>11,24; 16,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 31,67</t>
+          <t>11,68; 31,55</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>0,0; 8,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 11,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,92</t>
+          <t>1,53; 14,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 33,14</t>
+          <t>19,36; 33,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,91</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 34,37</t>
+          <t>7,83; 33,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 29,13</t>
+          <t>7,33; 28,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,32; 28,69</t>
+          <t>14,63; 28,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,85</t>
+          <t>3,73; 16,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 18,27</t>
+          <t>5,7; 17,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,97; 29,44</t>
+          <t>19,09; 29,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,74</t>
+          <t>0,38; 1,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,84</t>
+          <t>5,25; 8,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,35</t>
+          <t>5,05; 8,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,72; 33,07</t>
+          <t>27,36; 33,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,74</t>
+          <t>3,0; 6,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,66</t>
+          <t>10,69; 15,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,62</t>
+          <t>12,01; 17,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 21,38</t>
+          <t>8,02; 21,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,53</t>
+          <t>1,83; 3,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 11,29</t>
+          <t>8,05; 11,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 11,92</t>
+          <t>8,71; 11,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 26,4</t>
+          <t>15,18; 26,35</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>869; 8071</t>
+          <t>877; 8264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13722; 34279</t>
+          <t>13321; 34056</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10390; 27200</t>
+          <t>11108; 27634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74310; 101025</t>
+          <t>73940; 100508</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9271; 24476</t>
+          <t>9583; 25892</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25260; 49378</t>
+          <t>24252; 48796</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35018; 62593</t>
+          <t>35185; 64328</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49061; 69190</t>
+          <t>48447; 68821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12386; 29754</t>
+          <t>12669; 31033</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44180; 79516</t>
+          <t>43329; 74436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50716; 84345</t>
+          <t>49061; 82214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>129348; 162904</t>
+          <t>126920; 159699</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6107</t>
+          <t>0; 6417</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24644; 49183</t>
+          <t>24760; 48138</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26350; 49053</t>
+          <t>26674; 49848</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113698; 144813</t>
+          <t>113318; 146051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5245; 17511</t>
+          <t>5127; 18790</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41603; 66367</t>
+          <t>41794; 67533</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39221; 66976</t>
+          <t>39637; 67691</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25171; 140977</t>
+          <t>26849; 141022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6507; 21710</t>
+          <t>6765; 21126</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75102; 108643</t>
+          <t>73361; 108092</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71857; 107522</t>
+          <t>72509; 109130</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>98855; 277422</t>
+          <t>102341; 276329</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5289</t>
+          <t>0; 5247</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4757</t>
+          <t>0; 5065</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1043; 11035</t>
+          <t>1060; 9881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20680; 35900</t>
+          <t>20971; 35994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4910</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2438; 12226</t>
+          <t>2787; 11928</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4505; 15374</t>
+          <t>3871; 14792</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10590; 21225</t>
+          <t>10823; 21184</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7155</t>
+          <t>0; 5916</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3126; 14493</t>
+          <t>3030; 13136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6814; 22305</t>
+          <t>6957; 20901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34577; 53679</t>
+          <t>34797; 53516</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2732; 12874</t>
+          <t>2795; 13718</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44746; 76908</t>
+          <t>45649; 77051</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44719; 74952</t>
+          <t>45300; 76799</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221612; 264341</t>
+          <t>218724; 264824</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18477; 38851</t>
+          <t>17283; 39179</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78783; 116333</t>
+          <t>79448; 116127</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89137; 129602</t>
+          <t>88383; 130874</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82184; 199918</t>
+          <t>75010; 199601</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23706; 46446</t>
+          <t>23990; 48784</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132340; 182109</t>
+          <t>129928; 178829</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>142494; 194706</t>
+          <t>142246; 190674</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>278943; 457869</t>
+          <t>263369; 457037</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$otras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,62</t>
+          <t>0,17; 1,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,2</t>
+          <t>2,45; 6,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,27</t>
+          <t>2,56; 6,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,74; 33,63</t>
+          <t>25,01; 33,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,76</t>
+          <t>2,0; 5,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,09</t>
+          <t>4,63; 9,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 15,12</t>
+          <t>8,45; 15,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,83; 18,23</t>
+          <t>12,89; 18,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,23</t>
+          <t>1,29; 2,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,86</t>
+          <t>4,05; 7,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,49</t>
+          <t>5,8; 9,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,76; 23,61</t>
+          <t>19,32; 24,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 17,48</t>
+          <t>9,16; 17,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 12,86</t>
+          <t>6,73; 12,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,89; 37,24</t>
+          <t>29,63; 38,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 22,11</t>
+          <t>5,86; 22,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,49; 39,57</t>
+          <t>25,15; 39,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 26,3</t>
+          <t>15,53; 25,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 29,15</t>
+          <t>23,58; 32,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,4</t>
+          <t>2,61; 8,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 24,23</t>
+          <t>16,38; 24,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 16,92</t>
+          <t>10,99; 16,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 31,55</t>
+          <t>28,4; 34,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,65</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 9,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,26</t>
+          <t>1,5; 16,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,36; 33,22</t>
+          <t>19,39; 33,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 33,53</t>
+          <t>6,87; 34,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 28,03</t>
+          <t>7,31; 27,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,63; 28,64</t>
+          <t>14,54; 29,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 16,18</t>
+          <t>3,74; 17,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 17,12</t>
+          <t>5,26; 17,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 29,35</t>
+          <t>18,98; 29,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,86</t>
+          <t>0,37; 1,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,86</t>
+          <t>5,22; 8,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,56</t>
+          <t>5,02; 8,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,36; 33,13</t>
+          <t>27,88; 33,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,8</t>
+          <t>3,25; 6,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 15,63</t>
+          <t>10,51; 15,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,79</t>
+          <t>12,07; 17,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 21,34</t>
+          <t>18,84; 23,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,71</t>
+          <t>1,8; 3,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,09</t>
+          <t>8,19; 11,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,68</t>
+          <t>8,67; 11,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 26,35</t>
+          <t>24,44; 28,05</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86331</t>
+          <t>94309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58036</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>159118</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>877; 8264</t>
+          <t>874; 8724</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13321; 34056</t>
+          <t>13449; 33844</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11108; 27634</t>
+          <t>11285; 27577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73940; 100508</t>
+          <t>80226; 108884</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9583; 25892</t>
+          <t>9007; 23905</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24252; 48796</t>
+          <t>24853; 48625</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35185; 64328</t>
+          <t>35933; 64267</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48447; 68821</t>
+          <t>52977; 77182</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12669; 31033</t>
+          <t>12431; 28326</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43329; 74436</t>
+          <t>43935; 76604</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49061; 82214</t>
+          <t>50194; 82319</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>126920; 159699</t>
+          <t>141374; 177335</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128294</t>
+          <t>143540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77836</t>
+          <t>84785</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>206130</t>
+          <t>228325</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6417</t>
+          <t>0; 6761</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24760; 48138</t>
+          <t>25231; 48700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26674; 49848</t>
+          <t>26095; 49004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113318; 146051</t>
+          <t>126760; 163898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5127; 18790</t>
+          <t>4983; 18840</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41794; 67533</t>
+          <t>42911; 68007</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39637; 67691</t>
+          <t>39957; 65784</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26849; 141022</t>
+          <t>71820; 98739</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6765; 21126</t>
+          <t>6558; 21607</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73361; 108092</t>
+          <t>73089; 108400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72509; 109130</t>
+          <t>70893; 108459</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>102341; 276329</t>
+          <t>208004; 249815</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43277</t>
+          <t>50456</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5247</t>
+          <t>0; 4936</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5065</t>
+          <t>0; 4549</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1060; 9881</t>
+          <t>1042; 11285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20971; 35994</t>
+          <t>23838; 40860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4967</t>
+          <t>0; 5264</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2787; 11928</t>
+          <t>2445; 12234</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3871; 14792</t>
+          <t>3860; 14479</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10823; 21184</t>
+          <t>12459; 25235</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5916</t>
+          <t>0; 6788</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3030; 13136</t>
+          <t>3034; 14014</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6957; 20901</t>
+          <t>6420; 21145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34797; 53516</t>
+          <t>39605; 60817</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>269735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>151435</t>
+          <t>168164</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>393774</t>
+          <t>437899</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2795; 13718</t>
+          <t>2753; 12746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45649; 77051</t>
+          <t>45409; 77814</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45300; 76799</t>
+          <t>45014; 75196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>218724; 264824</t>
+          <t>242942; 294537</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17283; 39179</t>
+          <t>18706; 40171</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79448; 116127</t>
+          <t>78119; 114807</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88383; 130874</t>
+          <t>88794; 129417</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75010; 199601</t>
+          <t>150945; 186161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23990; 48784</t>
+          <t>23649; 46759</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129928; 178829</t>
+          <t>132185; 182943</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>142246; 190674</t>
+          <t>141609; 190709</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>263369; 457037</t>
+          <t>408863; 469291</t>
         </is>
       </c>
     </row>
